--- a/artfynd/A 33612-2023 artfynd.xlsx
+++ b/artfynd/A 33612-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33612-2023 artfynd.xlsx
+++ b/artfynd/A 33612-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85369678</v>
+        <v>85369677</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408279.9813889562</v>
+        <v>408056</v>
       </c>
       <c r="R2" t="n">
-        <v>6373052.043868875</v>
+        <v>6373048</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85369723</v>
+        <v>85369678</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408045.743314093</v>
+        <v>408280</v>
       </c>
       <c r="R3" t="n">
-        <v>6373056.251845601</v>
+        <v>6373052</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85369687</v>
+        <v>85369679</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408113.7664595091</v>
+        <v>408256</v>
       </c>
       <c r="R4" t="n">
-        <v>6373062.780928965</v>
+        <v>6373036</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85369727</v>
+        <v>85369680</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408314.1981940292</v>
+        <v>408293</v>
       </c>
       <c r="R5" t="n">
-        <v>6372896.964997643</v>
+        <v>6373039</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>85369693</v>
+        <v>85369681</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408236.1632643766</v>
+        <v>408348</v>
       </c>
       <c r="R6" t="n">
-        <v>6373043.891116051</v>
+        <v>6373042</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,19 +1131,9 @@
           <t>2019-11-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85369686</v>
+        <v>85369723</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408140.9806648162</v>
+        <v>408046</v>
       </c>
       <c r="R7" t="n">
-        <v>6373122.920758393</v>
+        <v>6373056</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1308,19 +1228,9 @@
           <t>2020-05-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>85369679</v>
+        <v>85369726</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408255.9154321239</v>
+        <v>408255</v>
       </c>
       <c r="R8" t="n">
-        <v>6373035.91889166</v>
+        <v>6372849</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>85369717</v>
+        <v>85369727</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408277.1140194317</v>
+        <v>408314</v>
       </c>
       <c r="R9" t="n">
-        <v>6373068.237910775</v>
+        <v>6372897</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>85369726</v>
+        <v>85369699</v>
       </c>
       <c r="B10" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408254.9323817217</v>
+        <v>408137</v>
       </c>
       <c r="R10" t="n">
-        <v>6372848.833989399</v>
+        <v>6373079</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,19 +1519,9 @@
           <t>2020-05-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>85369688</v>
+        <v>85369700</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408349.9704625974</v>
+        <v>408412</v>
       </c>
       <c r="R11" t="n">
-        <v>6373026.273590649</v>
+        <v>6373009</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1756,19 +1616,9 @@
           <t>2019-11-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>85369697</v>
+        <v>85369710</v>
       </c>
       <c r="B12" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408317.2533979248</v>
+        <v>408008</v>
       </c>
       <c r="R12" t="n">
-        <v>6372865.173583533</v>
+        <v>6373041</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1868,19 +1713,9 @@
           <t>2020-05-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,37 +1743,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>85369719</v>
+        <v>85369711</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408339.8008536783</v>
+        <v>408254</v>
       </c>
       <c r="R13" t="n">
-        <v>6373029.190771578</v>
+        <v>6372993</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1981,27 +1811,18 @@
           <t>2019-11-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-11-02</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2020,15 +1841,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>85369692</v>
+        <v>85369674</v>
       </c>
       <c r="B14" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2036,21 +1852,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408245.982503346</v>
+        <v>408396</v>
       </c>
       <c r="R14" t="n">
-        <v>6373073.2405129</v>
+        <v>6372952</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2090,22 +1906,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-11-03</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-11-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,12 +1941,7 @@
         <v>85369684</v>
       </c>
       <c r="B15" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,10 +1973,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408188.0270283798</v>
+        <v>408188</v>
       </c>
       <c r="R15" t="n">
-        <v>6373083.149290075</v>
+        <v>6373083</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2205,19 +2006,9 @@
           <t>2020-05-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,37 +2035,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>85369681</v>
+        <v>85369686</v>
       </c>
       <c r="B16" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2284,10 +2070,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408348.1675467768</v>
+        <v>408141</v>
       </c>
       <c r="R16" t="n">
-        <v>6373041.906058558</v>
+        <v>6373123</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2314,22 +2100,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,15 +2132,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>85369690</v>
+        <v>85369687</v>
       </c>
       <c r="B17" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408269.9121223948</v>
+        <v>408114</v>
       </c>
       <c r="R17" t="n">
-        <v>6372844.195097564</v>
+        <v>6373063</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2429,19 +2200,9 @@
           <t>2020-05-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,37 +2229,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>85369680</v>
+        <v>85369688</v>
       </c>
       <c r="B18" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2508,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408293.1514765519</v>
+        <v>408350</v>
       </c>
       <c r="R18" t="n">
-        <v>6373038.843612084</v>
+        <v>6373026</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2541,19 +2297,9 @@
           <t>2019-11-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,37 +2326,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>85369677</v>
+        <v>85369689</v>
       </c>
       <c r="B19" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2620,10 +2361,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408055.7913202449</v>
+        <v>408400</v>
       </c>
       <c r="R19" t="n">
-        <v>6373047.960169917</v>
+        <v>6373004</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2650,22 +2391,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,15 +2423,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>85369718</v>
+        <v>85369690</v>
       </c>
       <c r="B20" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,21 +2434,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2732,10 +2458,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408371.8708756335</v>
+        <v>408270</v>
       </c>
       <c r="R20" t="n">
-        <v>6372994.059093243</v>
+        <v>6372844</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2762,22 +2488,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,15 +2520,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>85369674</v>
+        <v>85369691</v>
       </c>
       <c r="B21" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,21 +2531,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2810</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2844,10 +2555,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408396.2461978656</v>
+        <v>408264</v>
       </c>
       <c r="R21" t="n">
-        <v>6372952.110901151</v>
+        <v>6372810</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2874,22 +2585,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2916,15 +2617,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>85369711</v>
+        <v>85369692</v>
       </c>
       <c r="B22" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2932,21 +2628,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2590</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2956,10 +2652,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408253.8699032828</v>
+        <v>408246</v>
       </c>
       <c r="R22" t="n">
-        <v>6372992.952623541</v>
+        <v>6373073</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2986,22 +2682,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3010,7 +2696,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3029,15 +2714,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>85369699</v>
+        <v>85369693</v>
       </c>
       <c r="B23" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3045,21 +2725,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2569</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3069,10 +2749,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408136.756011539</v>
+        <v>408236</v>
       </c>
       <c r="R23" t="n">
-        <v>6373078.929268647</v>
+        <v>6373044</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3099,22 +2779,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3141,15 +2811,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104322542</v>
+        <v>85369697</v>
       </c>
       <c r="B24" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,20 +2840,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lövömosse, Tranemo, Vg</t>
+          <t>Lövömosse, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408053.8120006596</v>
+        <v>408317</v>
       </c>
       <c r="R24" t="n">
-        <v>6373031.875289131</v>
+        <v>6372865</v>
       </c>
       <c r="S24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3212,22 +2876,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-10-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,6 +2890,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3254,15 +2909,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104322617</v>
+        <v>104322542</v>
       </c>
       <c r="B25" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,38 +2920,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tranemo, Vg</t>
+          <t>Lövömosse, Tranemo, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408054.0016762458</v>
+        <v>408054</v>
       </c>
       <c r="R25" t="n">
-        <v>6373064.130096477</v>
+        <v>6373032</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3330,7 +2980,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3340,7 +2990,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,32 +3017,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133865552</v>
+        <v>85369719</v>
       </c>
       <c r="B26" t="n">
-        <v>57972</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3402,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408246</v>
+        <v>408340</v>
       </c>
       <c r="R26" t="n">
-        <v>6373073</v>
+        <v>6373029</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3432,22 +3082,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2019-11-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133865575</v>
+        <v>133865552</v>
       </c>
       <c r="B27" t="n">
-        <v>57776</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3485,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102118</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3539,22 +3179,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>03:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>03:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3581,10 +3221,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133865546</v>
+        <v>104322617</v>
       </c>
       <c r="B28" t="n">
-        <v>57816</v>
+        <v>5179</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,42 +3232,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102621</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lövömosse, Vg</t>
+          <t>Tranemo, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408246</v>
+        <v>408055</v>
       </c>
       <c r="R28" t="n">
-        <v>6373073</v>
+        <v>6373064</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3651,22 +3287,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3690,6 +3326,322 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133865575</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lövömosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>408246</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6373073</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mossebo</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>85369718</v>
+      </c>
+      <c r="B30" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lövömosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>408372</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6372994</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mossebo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2019-11-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2019-11-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133865546</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57816</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lövömosse, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>408246</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6373073</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tranemo</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mossebo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Thomas Tranefors</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33612-2023 artfynd.xlsx
+++ b/artfynd/A 33612-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369680</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369723</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369726</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369727</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369700</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369710</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1741,6 +1796,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369711</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1838,6 +1898,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369674</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1935,6 +2000,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369687</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2032,6 +2102,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369688</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2129,6 +2204,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369689</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2226,6 +2306,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369690</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2323,6 +2408,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369691</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2420,6 +2510,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369693</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2518,6 +2613,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369697</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2626,6 +2726,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104322542</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2723,6 +2828,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369719</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2831,6 +2941,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104322617</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2928,6 +3043,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369718</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3025,6 +3145,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369699</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3122,6 +3247,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369684</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3219,6 +3349,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369686</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3316,6 +3451,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85369692</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3423,6 +3563,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133865552</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3530,6 +3675,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133865575</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3642,8 +3792,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133865546</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>